--- a/www/terminologies/ValueSet-JDV-J130-CNAMAmeliSecteurConventionnement-RASS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J130-CNAMAmeliSecteurConventionnement-RASS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20201127120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-11-27T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,28 +99,28 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>nc</t>
+    <t>0</t>
   </si>
   <si>
     <t>Non conventionné</t>
   </si>
   <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>Secteur 1 ou conventionné</t>
-  </si>
-  <si>
-    <t>c2</t>
-  </si>
-  <si>
-    <t>Secteur 1 ou conventionné avec droit au dépassement permanent</t>
-  </si>
-  <si>
-    <t>c3</t>
-  </si>
-  <si>
-    <t>Secteur 2</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Conventionné</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Conventionné avec dépassement</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Conventionné avec honoraires libres</t>
   </si>
   <si>
     <t/>
